--- a/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,03</t>
+          <t>0,71; 2,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,57</t>
+          <t>1,26; 4,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,23</t>
+          <t>1,73; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,06</t>
+          <t>2,24; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,49</t>
+          <t>2,04; 5,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,76</t>
+          <t>2,41; 6,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,0</t>
+          <t>1,01; 3,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,19</t>
+          <t>3,66; 10,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,58</t>
+          <t>1,57; 3,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,64</t>
+          <t>2,24; 4,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,91</t>
+          <t>1,59; 3,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,5</t>
+          <t>3,54; 8,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,44</t>
+          <t>1,35; 3,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,89</t>
+          <t>3,43; 7,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,53</t>
+          <t>1,91; 4,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,55</t>
+          <t>6,26; 14,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,07</t>
+          <t>1,48; 3,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,13</t>
+          <t>2,51; 5,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,79</t>
+          <t>1,27; 3,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,8</t>
+          <t>1,63; 5,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,31</t>
+          <t>1,64; 3,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,74</t>
+          <t>3,42; 5,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,72</t>
+          <t>1,85; 3,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,44</t>
+          <t>4,23; 8,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,21</t>
+          <t>2,77; 6,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,48</t>
+          <t>3,63; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,25</t>
+          <t>2,36; 5,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,67</t>
+          <t>2,25; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,77</t>
+          <t>3,16; 6,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,61</t>
+          <t>5,59; 9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,43</t>
+          <t>2,67; 5,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,98</t>
+          <t>3,64; 7,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,79</t>
+          <t>3,36; 5,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,82</t>
+          <t>5,17; 7,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,92</t>
+          <t>2,79; 4,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,8</t>
+          <t>3,46; 5,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,62</t>
+          <t>3,54; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,74</t>
+          <t>4,68; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,62</t>
+          <t>5,33; 9,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,36</t>
+          <t>3,26; 11,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 11,14</t>
+          <t>6,34; 10,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,41</t>
+          <t>7,17; 12,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,84</t>
+          <t>5,16; 9,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,68</t>
+          <t>6,91; 10,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,43</t>
+          <t>5,29; 8,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,98</t>
+          <t>6,67; 9,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,56</t>
+          <t>5,71; 8,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,14</t>
+          <t>4,97; 10,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,37</t>
+          <t>6,63; 12,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 14,2</t>
+          <t>8,09; 14,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,76</t>
+          <t>6,37; 11,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,38; 19,49</t>
+          <t>13,3; 19,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,11</t>
+          <t>5,63; 11,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 15,17</t>
+          <t>8,54; 15,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 16,58</t>
+          <t>10,28; 16,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,33</t>
+          <t>8,62; 12,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,4</t>
+          <t>6,64; 11,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,35</t>
+          <t>9,14; 13,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 13,39</t>
+          <t>8,84; 13,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 14,98</t>
+          <t>11,59; 15,13</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,41</t>
+          <t>5,55; 12,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,73</t>
+          <t>9,63; 18,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,73</t>
+          <t>5,11; 10,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 16,73</t>
+          <t>10,74; 16,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,89</t>
+          <t>6,62; 11,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,81</t>
+          <t>8,21; 15,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,46</t>
+          <t>5,97; 11,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,6; 75,87</t>
+          <t>13,41; 73,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,18</t>
+          <t>6,72; 11,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 15,12</t>
+          <t>9,95; 15,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,16</t>
+          <t>6,34; 10,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 62,73</t>
+          <t>13,32; 63,3</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 16,15</t>
+          <t>8,04; 16,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,81</t>
+          <t>11,2; 21,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,86</t>
+          <t>4,84; 11,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,9; 31,12</t>
+          <t>22,77; 31,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,56</t>
+          <t>8,9; 16,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,62</t>
+          <t>15,67; 24,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,45</t>
+          <t>10,61; 18,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,76; 34,29</t>
+          <t>28,2; 34,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,9</t>
+          <t>9,52; 15,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,59</t>
+          <t>14,77; 21,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 14,49</t>
+          <t>8,97; 14,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,02; 32,27</t>
+          <t>26,99; 32,03</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,83</t>
+          <t>4,3; 5,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,27</t>
+          <t>6,48; 8,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,36</t>
+          <t>4,78; 6,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 11,76</t>
+          <t>8,11; 11,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,13</t>
+          <t>5,49; 7,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 10,04</t>
+          <t>8,12; 10,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,77</t>
+          <t>6,07; 7,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,52; 31,24</t>
+          <t>10,51; 31,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,25</t>
+          <t>5,13; 6,22</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,89</t>
+          <t>7,56; 8,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,89</t>
+          <t>5,61; 6,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,32; 22,62</t>
+          <t>10,27; 21,01</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3666; 14979</t>
+          <t>3526; 14353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5786; 20765</t>
+          <t>5709; 20417</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6966; 21943</t>
+          <t>7240; 22677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9326; 36254</t>
+          <t>8956; 35071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9271; 25673</t>
+          <t>9547; 25206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10921; 29102</t>
+          <t>10378; 27355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3811; 15817</t>
+          <t>4005; 15326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11740; 35058</t>
+          <t>11465; 34436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16146; 34400</t>
+          <t>15103; 33750</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20234; 41063</t>
+          <t>19832; 41326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13689; 31853</t>
+          <t>12973; 31533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24356; 60645</t>
+          <t>25254; 60125</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9800; 25304</t>
+          <t>9899; 25212</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23905; 47335</t>
+          <t>23585; 48410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10891; 26729</t>
+          <t>11256; 26958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26503; 61633</t>
+          <t>26514; 60518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9049; 25481</t>
+          <t>9264; 24699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15700; 37378</t>
+          <t>15343; 34955</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6794; 21352</t>
+          <t>7147; 21601</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7458; 24560</t>
+          <t>8333; 25606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22904; 45028</t>
+          <t>22270; 43417</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44838; 74515</t>
+          <t>44397; 77449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21246; 42915</t>
+          <t>21379; 43741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38799; 78985</t>
+          <t>39560; 79778</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18066; 39672</t>
+          <t>17676; 39894</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25812; 50987</t>
+          <t>24742; 49083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15647; 35098</t>
+          <t>15816; 35688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12341; 30404</t>
+          <t>12077; 29790</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21897; 46707</t>
+          <t>21777; 44989</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39548; 68317</t>
+          <t>39701; 68357</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17634; 35902</t>
+          <t>17687; 36584</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22055; 41321</t>
+          <t>21561; 42702</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45633; 76855</t>
+          <t>44584; 75978</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71083; 108850</t>
+          <t>72019; 110651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37014; 65400</t>
+          <t>37060; 65263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38427; 65429</t>
+          <t>39095; 65115</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18777; 39583</t>
+          <t>18375; 39451</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28521; 53726</t>
+          <t>28788; 55329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33831; 62169</t>
+          <t>34426; 61220</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28813; 100876</t>
+          <t>28922; 99868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30859; 57442</t>
+          <t>32698; 56652</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45938; 76470</t>
+          <t>44203; 76540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32621; 57359</t>
+          <t>33478; 60198</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50023; 76103</t>
+          <t>49235; 75332</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55935; 87215</t>
+          <t>54720; 89197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80474; 122826</t>
+          <t>82071; 121218</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73690; 110879</t>
+          <t>73988; 112621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>77798; 162358</t>
+          <t>79605; 163737</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25337; 47844</t>
+          <t>25651; 49336</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33663; 60960</t>
+          <t>34757; 60885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30387; 56191</t>
+          <t>30445; 56223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75081; 109394</t>
+          <t>74670; 107001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22409; 44872</t>
+          <t>22724; 46337</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39086; 67922</t>
+          <t>38228; 67604</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50577; 82369</t>
+          <t>51074; 82164</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46536; 67550</t>
+          <t>47236; 67245</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52237; 82222</t>
+          <t>52500; 87641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79306; 117122</t>
+          <t>80213; 119857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88770; 130515</t>
+          <t>86202; 128506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>128588; 166197</t>
+          <t>128586; 167792</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16674; 36324</t>
+          <t>16247; 35742</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29463; 58019</t>
+          <t>29836; 57068</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17496; 35869</t>
+          <t>17091; 36413</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39341; 61591</t>
+          <t>39539; 59957</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21091; 40790</t>
+          <t>22714; 41076</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28540; 52444</t>
+          <t>29054; 53893</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21756; 43285</t>
+          <t>22555; 44809</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82713; 461540</t>
+          <t>81594; 446265</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42786; 71081</t>
+          <t>42718; 71878</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65338; 100366</t>
+          <t>66018; 102285</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43015; 72331</t>
+          <t>45147; 72976</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>130901; 612562</t>
+          <t>130037; 618118</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16185; 33905</t>
+          <t>16869; 34552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27705; 54497</t>
+          <t>27992; 53399</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11795; 27906</t>
+          <t>12438; 28745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64749; 88004</t>
+          <t>64383; 88933</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30578; 55312</t>
+          <t>29703; 55335</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60363; 91867</t>
+          <t>60950; 93931</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40700; 73811</t>
+          <t>42456; 75058</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>118207; 146033</t>
+          <t>120073; 147699</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51910; 81042</t>
+          <t>51766; 83252</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94454; 137925</t>
+          <t>94346; 137054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60271; 95253</t>
+          <t>58928; 93383</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>191491; 228637</t>
+          <t>191248; 226993</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>139518; 191126</t>
+          <t>140911; 188514</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>219117; 283385</t>
+          <t>222019; 282813</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>161060; 215899</t>
+          <t>162097; 216780</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>288845; 406715</t>
+          <t>280643; 412039</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>183046; 240842</t>
+          <t>185394; 242778</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>287725; 357100</t>
+          <t>289062; 360613</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>214419; 275554</t>
+          <t>215180; 277386</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>390677; 1159719</t>
+          <t>390238; 1157341</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>338131; 415727</t>
+          <t>341330; 414212</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>527507; 620899</t>
+          <t>527858; 621491</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>392163; 478357</t>
+          <t>389233; 476535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>739944; 1622589</t>
+          <t>736831; 1507037</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,91</t>
+          <t>0,73; 2,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,5</t>
+          <t>1,28; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,41</t>
+          <t>1,62; 5,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,77</t>
+          <t>2,09; 8,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,39</t>
+          <t>1,95; 5,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,36</t>
+          <t>2,56; 6,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,87</t>
+          <t>0,97; 4,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,99</t>
+          <t>3,81; 11,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,51</t>
+          <t>1,59; 3,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,67</t>
+          <t>2,18; 4,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,87</t>
+          <t>1,76; 3,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,43</t>
+          <t>3,6; 8,04</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,43</t>
+          <t>1,34; 3,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,05</t>
+          <t>3,51; 6,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,57</t>
+          <t>1,89; 4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,29</t>
+          <t>5,6; 12,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,95</t>
+          <t>1,55; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,73</t>
+          <t>2,56; 6,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,83</t>
+          <t>1,33; 3,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,0</t>
+          <t>2,45; 6,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,19</t>
+          <t>1,7; 3,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,97</t>
+          <t>3,44; 5,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,79</t>
+          <t>1,83; 3,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,53</t>
+          <t>4,52; 8,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,25</t>
+          <t>2,75; 6,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,2</t>
+          <t>3,78; 7,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,33</t>
+          <t>2,31; 5,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,55</t>
+          <t>2,16; 5,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,52</t>
+          <t>3,17; 6,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,62</t>
+          <t>5,48; 9,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,53</t>
+          <t>2,57; 5,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,21</t>
+          <t>4,39; 7,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,72</t>
+          <t>3,35; 5,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,94</t>
+          <t>5,09; 7,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,91</t>
+          <t>2,82; 4,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,77</t>
+          <t>3,65; 5,94</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,6</t>
+          <t>3,49; 7,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,0</t>
+          <t>4,69; 8,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,48</t>
+          <t>5,22; 9,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,25</t>
+          <t>8,13; 12,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,99</t>
+          <t>6,32; 11,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 12,42</t>
+          <t>7,5; 12,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,27</t>
+          <t>5,09; 9,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,57</t>
+          <t>7,78; 11,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,62</t>
+          <t>5,38; 8,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,85</t>
+          <t>6,62; 10,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,7</t>
+          <t>5,62; 8,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 10,23</t>
+          <t>8,27; 11,21</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,76</t>
+          <t>6,42; 12,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 14,18</t>
+          <t>8,06; 14,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,76</t>
+          <t>6,29; 11,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 19,07</t>
+          <t>12,88; 18,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,47</t>
+          <t>5,51; 11,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,1</t>
+          <t>8,55; 14,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,54</t>
+          <t>10,1; 16,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,27</t>
+          <t>9,17; 13,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,08</t>
+          <t>6,74; 10,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,66</t>
+          <t>9,19; 13,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,18</t>
+          <t>8,94; 13,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 15,13</t>
+          <t>11,64; 15,22</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,22</t>
+          <t>5,87; 12,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,63; 18,42</t>
+          <t>9,97; 18,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,89</t>
+          <t>5,26; 10,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 16,29</t>
+          <t>10,77; 16,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,98</t>
+          <t>6,47; 12,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 15,22</t>
+          <t>8,4; 15,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,86</t>
+          <t>5,71; 11,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 73,35</t>
+          <t>12,27; 17,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,31</t>
+          <t>6,71; 11,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,41</t>
+          <t>10,21; 15,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,25</t>
+          <t>6,3; 10,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 63,3</t>
+          <t>12,22; 16,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,46</t>
+          <t>7,85; 16,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 21,37</t>
+          <t>10,98; 21,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,18</t>
+          <t>4,75; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,77; 31,45</t>
+          <t>22,4; 30,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 16,57</t>
+          <t>9,05; 16,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,67; 24,15</t>
+          <t>15,61; 24,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 18,76</t>
+          <t>10,58; 18,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,2; 34,68</t>
+          <t>28,11; 34,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,52; 15,31</t>
+          <t>9,75; 15,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,77; 21,45</t>
+          <t>15,08; 21,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,21</t>
+          <t>9,1; 14,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,99; 32,03</t>
+          <t>26,81; 31,77</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,75</t>
+          <t>4,23; 5,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,25</t>
+          <t>6,37; 8,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,39</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,91</t>
+          <t>9,81; 11,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,18</t>
+          <t>5,4; 7,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,13</t>
+          <t>8,08; 10,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,83</t>
+          <t>6,01; 7,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,51; 31,18</t>
+          <t>10,65; 12,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,22</t>
+          <t>5,08; 6,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,9</t>
+          <t>7,56; 8,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 6,87</t>
+          <t>5,65; 6,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,01</t>
+          <t>10,52; 11,87</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>43119</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3526; 14353</t>
+          <t>3601; 14463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5709; 20417</t>
+          <t>5810; 22293</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7240; 22677</t>
+          <t>6816; 22569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8956; 35071</t>
+          <t>8522; 34988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9547; 25206</t>
+          <t>9104; 24686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10378; 27355</t>
+          <t>11033; 27586</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4005; 15326</t>
+          <t>3827; 16215</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11465; 34436</t>
+          <t>13812; 40886</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15103; 33750</t>
+          <t>15251; 34733</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19832; 41326</t>
+          <t>19285; 41086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12973; 31533</t>
+          <t>14308; 31111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25254; 60125</t>
+          <t>27699; 61953</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56266</t>
+          <t>60483</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9899; 25212</t>
+          <t>9859; 26972</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23585; 48410</t>
+          <t>24092; 46769</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11256; 26958</t>
+          <t>11188; 29047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26514; 60518</t>
+          <t>26702; 60913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9264; 24699</t>
+          <t>9690; 26029</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15343; 34955</t>
+          <t>15618; 36967</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7147; 21601</t>
+          <t>7516; 22065</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8333; 25606</t>
+          <t>12285; 30338</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22270; 43417</t>
+          <t>23149; 44456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44397; 77449</t>
+          <t>44602; 74129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21379; 43741</t>
+          <t>21155; 42690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39560; 79778</t>
+          <t>44257; 83003</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>58643</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17676; 39894</t>
+          <t>17538; 39762</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24742; 49083</t>
+          <t>25776; 50169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15816; 35688</t>
+          <t>15431; 35303</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12077; 29790</t>
+          <t>13391; 33137</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21777; 44989</t>
+          <t>21863; 46136</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39701; 68357</t>
+          <t>38954; 68231</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17687; 36584</t>
+          <t>16972; 35988</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21561; 42702</t>
+          <t>27360; 47744</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44584; 75978</t>
+          <t>44463; 77160</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72019; 110651</t>
+          <t>70896; 108088</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37060; 65263</t>
+          <t>37490; 66088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39095; 65115</t>
+          <t>45426; 73939</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66671</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>139968</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18375; 39451</t>
+          <t>18119; 41001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28788; 55329</t>
+          <t>28831; 54280</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34426; 61220</t>
+          <t>33711; 60115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28922; 99868</t>
+          <t>56947; 90597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32698; 56652</t>
+          <t>32604; 56987</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44203; 76540</t>
+          <t>46191; 78736</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33478; 60198</t>
+          <t>33012; 59042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49235; 75332</t>
+          <t>57293; 81215</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54720; 89197</t>
+          <t>55640; 89528</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82071; 121218</t>
+          <t>81529; 126094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73988; 112621</t>
+          <t>72810; 114137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79605; 163737</t>
+          <t>118849; 161078</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90296</t>
+          <t>95379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57195</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>147490</t>
+          <t>162621</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25651; 49336</t>
+          <t>24811; 47705</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34757; 60885</t>
+          <t>34627; 61161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30445; 56223</t>
+          <t>30069; 56598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74670; 107001</t>
+          <t>78512; 113549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22724; 46337</t>
+          <t>22254; 45656</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38228; 67604</t>
+          <t>38270; 66624</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51074; 82164</t>
+          <t>50190; 81122</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47236; 67245</t>
+          <t>55807; 80523</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52500; 87641</t>
+          <t>53304; 84602</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80213; 119857</t>
+          <t>80575; 119659</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86202; 128506</t>
+          <t>87184; 129803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>128586; 167792</t>
+          <t>141817; 185411</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>262876</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>118817</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16247; 35742</t>
+          <t>17178; 36120</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29836; 57068</t>
+          <t>30896; 57666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17091; 36413</t>
+          <t>17591; 36302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39539; 59957</t>
+          <t>43831; 66692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22714; 41076</t>
+          <t>22173; 42277</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29054; 53893</t>
+          <t>29737; 55865</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22555; 44809</t>
+          <t>21561; 42712</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81594; 446265</t>
+          <t>53875; 75550</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42718; 71878</t>
+          <t>42622; 70529</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66018; 102285</t>
+          <t>67791; 102494</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45147; 72976</t>
+          <t>44829; 76420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>130037; 618118</t>
+          <t>103385; 136059</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75873</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>132840</t>
+          <t>145408</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>208713</t>
+          <t>227441</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16869; 34552</t>
+          <t>16485; 33917</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27992; 53399</t>
+          <t>27434; 53681</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12438; 28745</t>
+          <t>12201; 27911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64383; 88933</t>
+          <t>69498; 95350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29703; 55335</t>
+          <t>30226; 56510</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60950; 93931</t>
+          <t>60727; 93627</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42456; 75058</t>
+          <t>42352; 74676</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>120073; 147699</t>
+          <t>130611; 160746</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51766; 83252</t>
+          <t>53018; 82405</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94346; 137054</t>
+          <t>96310; 137891</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58928; 93383</t>
+          <t>59805; 95242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>191248; 226993</t>
+          <t>207705; 246137</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>140911; 188514</t>
+          <t>138475; 189999</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>222019; 282813</t>
+          <t>218116; 285421</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>162097; 216780</t>
+          <t>163918; 217219</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>280643; 412039</t>
+          <t>346484; 422103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>185394; 242778</t>
+          <t>182438; 241226</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>289062; 360613</t>
+          <t>287533; 360504</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>215180; 277386</t>
+          <t>213063; 274503</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>390238; 1157341</t>
+          <t>398113; 463994</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>341330; 414212</t>
+          <t>338008; 411953</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>527858; 621491</t>
+          <t>527790; 627280</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>389233; 476535</t>
+          <t>392156; 470234</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>736831; 1507037</t>
+          <t>764914; 862677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
